--- a/data/trans_dic/DCD-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 14,84</t>
+          <t>10,28; 14,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 14,84</t>
+          <t>10,26; 14,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,57; 29,3</t>
+          <t>22,81; 29,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,84; 26,84</t>
+          <t>22,17; 27,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 24,04</t>
+          <t>18,85; 24,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,9; 46,47</t>
+          <t>40,88; 46,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,46; 20,87</t>
+          <t>17,62; 21,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 19,43</t>
+          <t>15,56; 19,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,2; 38,68</t>
+          <t>34,33; 38,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,0</t>
+          <t>4,06; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,3</t>
+          <t>4,36; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 12,38</t>
+          <t>7,2; 12,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 13,83</t>
+          <t>10,46; 13,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,97</t>
+          <t>9,15; 12,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,49</t>
+          <t>14,83; 22,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,26</t>
+          <t>7,36; 9,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,79</t>
+          <t>7,02; 8,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,8</t>
+          <t>11,93; 16,85</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,15</t>
+          <t>1,07; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,88</t>
+          <t>2,92; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,11</t>
+          <t>5,96; 9,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 13,05</t>
+          <t>7,35; 13,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,64</t>
+          <t>5,02; 9,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 22,3</t>
+          <t>17,02; 22,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,73</t>
+          <t>4,45; 7,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,55</t>
+          <t>4,49; 7,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 15,4</t>
+          <t>12,09; 15,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,55</t>
+          <t>5,9; 7,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,67</t>
+          <t>5,95; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 13,77</t>
+          <t>9,76; 13,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 17,5</t>
+          <t>15,12; 17,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,34</t>
+          <t>11,9; 14,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 26,66</t>
+          <t>20,07; 26,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 12,42</t>
+          <t>10,8; 12,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 10,74</t>
+          <t>9,28; 10,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 20,12</t>
+          <t>16,14; 20,02</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante</t>
+          <t>Población con dolor crónico discapacitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100749; 144682</t>
+          <t>100227; 143780</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75199; 111921</t>
+          <t>77396; 112357</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116207; 150880</t>
+          <t>117442; 151889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>292174; 359098</t>
+          <t>296582; 362538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>185705; 239160</t>
+          <t>187451; 240437</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>309021; 351079</t>
+          <t>308849; 351349</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>403662; 482635</t>
+          <t>407436; 485588</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>273676; 339858</t>
+          <t>272117; 340967</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>434549; 491461</t>
+          <t>436153; 488337</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78066; 117826</t>
+          <t>79683; 118707</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88707; 130765</t>
+          <t>90628; 132002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173004; 283542</t>
+          <t>164935; 278522</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>184775; 243163</t>
+          <t>183916; 240494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>180577; 237985</t>
+          <t>181896; 239564</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>318244; 503224</t>
+          <t>331879; 504307</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>276369; 344610</t>
+          <t>273800; 345884</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>284821; 357390</t>
+          <t>285165; 357054</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>532178; 760919</t>
+          <t>540367; 762876</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5824; 19961</t>
+          <t>5172; 20147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15688; 37636</t>
+          <t>15953; 39085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39278; 65368</t>
+          <t>38569; 64237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32611; 59836</t>
+          <t>33718; 59938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28023; 52963</t>
+          <t>27584; 52327</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110584; 147282</t>
+          <t>112409; 149440</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41787; 72634</t>
+          <t>41834; 73105</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49801; 82746</t>
+          <t>49159; 83060</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>157763; 201333</t>
+          <t>158025; 203577</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198959; 258314</t>
+          <t>201634; 261359</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200819; 259046</t>
+          <t>201135; 262201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>334084; 475244</t>
+          <t>336878; 472634</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535781; 622143</t>
+          <t>537570; 633312</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>421505; 506472</t>
+          <t>420452; 508911</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>712815; 974185</t>
+          <t>733465; 979327</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>757468; 866106</t>
+          <t>753095; 862089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>638517; 742131</t>
+          <t>641486; 740657</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1158528; 1429816</t>
+          <t>1147027; 1422852</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DCD-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DCD-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,75</t>
+          <t>10,3; 14,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,89</t>
+          <t>10,02; 14,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,81; 29,5</t>
+          <t>21,54; 28,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,1</t>
+          <t>22,07; 26,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,85; 24,17</t>
+          <t>18,43; 24,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,88; 46,5</t>
+          <t>40,68; 45,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,0</t>
+          <t>17,54; 20,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 19,49</t>
+          <t>15,69; 19,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,33; 38,44</t>
+          <t>33,4; 37,78</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,04</t>
+          <t>4,01; 5,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,36</t>
+          <t>4,37; 6,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,16</t>
+          <t>10,03; 12,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 13,68</t>
+          <t>10,53; 13,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,05</t>
+          <t>9,16; 12,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 22,54</t>
+          <t>21,16; 24,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,29</t>
+          <t>7,39; 9,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,78</t>
+          <t>7,01; 8,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,85</t>
+          <t>15,96; 18,13</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,19</t>
+          <t>1,23; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,15</t>
+          <t>2,95; 7,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,93</t>
+          <t>6,01; 10,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,07</t>
+          <t>6,88; 12,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,53</t>
+          <t>5,08; 9,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,63</t>
+          <t>17,71; 23,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,78</t>
+          <t>4,48; 7,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,58</t>
+          <t>4,6; 7,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,57</t>
+          <t>12,49; 16,23</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,64</t>
+          <t>5,84; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,76</t>
+          <t>5,86; 7,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,69</t>
+          <t>11,78; 14,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 17,82</t>
+          <t>15,12; 17,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 14,41</t>
+          <t>11,96; 14,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 26,8</t>
+          <t>25,52; 28,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,36</t>
+          <t>10,84; 12,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 10,72</t>
+          <t>9,21; 10,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 20,02</t>
+          <t>19,18; 20,89</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133758</t>
+          <t>143299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>329675</t>
+          <t>355380</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>463433</t>
+          <t>498678</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100227; 143780</t>
+          <t>100380; 144059</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77396; 112357</t>
+          <t>75601; 111256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117442; 151889</t>
+          <t>124631; 163410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>296582; 362538</t>
+          <t>295238; 356764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>187451; 240437</t>
+          <t>183344; 241219</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>308849; 351349</t>
+          <t>334427; 377508</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>407436; 485588</t>
+          <t>405512; 481573</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>272117; 340967</t>
+          <t>274345; 339605</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>436153; 488337</t>
+          <t>467741; 529152</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238983</t>
+          <t>255304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>439904</t>
+          <t>492761</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>678887</t>
+          <t>748065</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79683; 118707</t>
+          <t>78700; 117091</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90628; 132002</t>
+          <t>90746; 132333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164935; 278522</t>
+          <t>223827; 288388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183916; 240494</t>
+          <t>185022; 243484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>181896; 239564</t>
+          <t>182193; 242392</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>331879; 504307</t>
+          <t>459440; 531285</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>273800; 345884</t>
+          <t>274966; 343494</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>285165; 357054</t>
+          <t>284810; 355603</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>540367; 762876</t>
+          <t>702534; 798005</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>56308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>129148</t>
+          <t>148377</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>180452</t>
+          <t>204685</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5172; 20147</t>
+          <t>5914; 20310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15953; 39085</t>
+          <t>16153; 38396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38569; 64237</t>
+          <t>42768; 71438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33718; 59938</t>
+          <t>31550; 59081</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27584; 52327</t>
+          <t>27884; 53374</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>112409; 149440</t>
+          <t>130182; 169580</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41834; 73105</t>
+          <t>42147; 74251</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49159; 83060</t>
+          <t>50399; 85071</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158025; 203577</t>
+          <t>180604; 234695</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>454911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>898727</t>
+          <t>996518</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1322772</t>
+          <t>1451429</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>201634; 261359</t>
+          <t>199805; 258046</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>201135; 262201</t>
+          <t>197851; 258644</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>336878; 472634</t>
+          <t>414744; 496011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>537570; 633312</t>
+          <t>537371; 622291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>420452; 508911</t>
+          <t>422415; 507100</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>733465; 979327</t>
+          <t>951645; 1044161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>753095; 862089</t>
+          <t>755693; 863594</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>641486; 740657</t>
+          <t>636686; 742295</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1147027; 1422852</t>
+          <t>1390575; 1514420</t>
         </is>
       </c>
     </row>
